--- a/apps/web/public/samples/supported_layouts.xlsx
+++ b/apps/web/public/samples/supported_layouts.xlsx
@@ -161,7 +161,7 @@
     <t>→ JSON record:  { employee_id, name, department, salary, hire_date }</t>
   </si>
   <si>
-    <t>→ Parser config:  orientation=row  |  header_row=1 (static)  |  data_start_row=2</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t>Table 1-1</t>
@@ -176,7 +176,7 @@
     <t>Each column = one record. Headers are fixed field names down the first column.</t>
   </si>
   <si>
-    <t>→ Parser config:  orientation=column  |  header_col=1 (static)  |  data_start_col=2</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t>Single Axis Dynamic - Table 1</t>
@@ -191,7 +191,7 @@
     <t>→ JSON record (after unpivot):  { month, sales }  — 'month'/'sales' are user-supplied field names</t>
   </si>
   <si>
-    <t>→ Parser config:  orientation=row  |  header_row=1 (dynamic)  |  row_label_col=1 (dynamic)</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t>Single Axis Dynamic - Table 1-1</t>
@@ -203,33 +203,7 @@
     <t>Transposed: month names run down the first column</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <i val="1"/>
-        <sz val="9"/>
-        <color indexed="15"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>→ JSON record (after unpivot):  { month, sales }  — same record shape as sheet 3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="1"/>
-        <sz val="9"/>
-        <color indexed="15"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>→ Parser config:  orientation=column  |  header_col=1 (dynamic)  |  col_label_row=1 (dynamic)</t>
-    </r>
+    <t xml:space="preserve">→ JSON record (after unpivot):  { month, sales }  — same record shape as sheet 3</t>
   </si>
   <si>
     <t>Pivot - Table 1</t>
@@ -271,43 +245,8 @@
     <t>Product 4</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <i val="1"/>
-        <sz val="9"/>
-        <color indexed="15"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">→ JSON record:  { account, product, year, revenue }  — static col names → fields; ‘year' is user-supplied column-label field name; 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="1"/>
-        <sz val="9"/>
-        <color indexed="15"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">     ‘revenue is user-supplied value-label field’</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="1"/>
-        <sz val="9"/>
-        <color indexed="15"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>→ Parser config:  orientation=row  |  header_row=1 (static)  |  row_label_col=1 (dynamic)  |  row_label_field=‘revenue’ | row_label_value=‘revenue’</t>
-    </r>
+    <t xml:space="preserve">→ JSON record:  { account, product, year, revenue }  — static col names → fields; ‘year' is user-supplied column-label field name; 
+     ‘revenue is user-supplied value-label field’</t>
   </si>
   <si>
     <t>Pivot - Table 1-1</t>
@@ -319,43 +258,8 @@
     <t>Transposed: headers run down the first column</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <i val="1"/>
-        <sz val="9"/>
-        <color indexed="15"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">→ JSON record:  { account, product, year, revenue }  — static col names → fields; ‘year' is user-supplied column-label field name; 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="1"/>
-        <sz val="9"/>
-        <color indexed="15"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">     ‘revenue is user-supplied value-label field’</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="1"/>
-        <sz val="9"/>
-        <color indexed="15"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>→ Parser config:  orientation=column  |  header_row=1 (static)  |  row_label_col=1 (dynamic)  |  row_label_field=‘revenue’ | row_label_value=‘revenue’</t>
-    </r>
+    <t xml:space="preserve">→ JSON record:  { account, product, year, revenue }  — static col names → fields; ‘year' is user-supplied column-label field name; 
+     ‘revenue is user-supplied value-label field’</t>
   </si>
   <si>
     <t>Crosstab - Table 1-1</t>
@@ -400,7 +304,7 @@
     <t>→ JSON record (after melt):  { team, severity, tickets }  — same record shape as sheet 7; field names now self-describing</t>
   </si>
   <si>
-    <t>→ Parser config:  orientation=both  |  row_label_col=1 (static)  |  col_label_row=1 (static)  |  corner=row_field_name</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t>Crosstab - Table 1</t>
@@ -415,7 +319,7 @@
     <t>→ JSON record (after melt):  { team, severity, tickets }  — all three field names are user-supplied</t>
   </si>
   <si>
-    <t>→ Parser config:  orientation=both  |  row_label_col=1 (dynamic)  |  col_label_row=1 (dynamic)  |  corner=blank</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t>Table 1-1-1</t>
@@ -499,8 +403,7 @@
     <t>→ JSON record (after melt):  { company, quarter, revenue, currency, scope, industry, hq }</t>
   </si>
   <si>
-    <t>→ Parser config:  orientation=both  |  row_label_col=1 (static)  |  col_label_col=1 (dynamic) |  
-     row_label_col=3 (dynamic)  | col_label_col=3 (dynamic) | corner=row_field_name</t>
+    <t xml:space="preserve"/>
   </si>
 </sst>
 </file>
